--- a/data/trans_dic/IP08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 19,26</t>
+          <t>5,9; 19,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,25; 35,3</t>
+          <t>17,08; 35,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 21,0</t>
+          <t>6,27; 20,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,78; 41,04</t>
+          <t>8,56; 41,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 28,76</t>
+          <t>11,99; 29,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 37,92</t>
+          <t>18,79; 38,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 22,23</t>
+          <t>7,99; 22,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 25,41</t>
+          <t>10,39; 26,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,91; 21,16</t>
+          <t>10,05; 21,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,76; 33,05</t>
+          <t>20,16; 33,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,1; 19,2</t>
+          <t>8,53; 19,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,67; 28,64</t>
+          <t>11,61; 29,59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 15,53</t>
+          <t>5,88; 15,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 16,6</t>
+          <t>7,36; 17,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,58</t>
+          <t>1,19; 7,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 10,93</t>
+          <t>2,37; 10,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 16,28</t>
+          <t>6,63; 15,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 16,81</t>
+          <t>6,82; 16,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,07</t>
+          <t>1,19; 6,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,57</t>
+          <t>3,74; 12,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 13,7</t>
+          <t>7,3; 14,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,95; 14,95</t>
+          <t>8,03; 15,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,89</t>
+          <t>1,73; 5,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,5</t>
+          <t>3,8; 9,69</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 15,03</t>
+          <t>3,01; 14,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 22,77</t>
+          <t>8,04; 22,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 14,32</t>
+          <t>3,11; 14,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 20,37</t>
+          <t>7,03; 21,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 13,4</t>
+          <t>2,69; 13,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 15,53</t>
+          <t>4,68; 15,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,75</t>
+          <t>0,94; 8,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 20,97</t>
+          <t>6,7; 20,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,81</t>
+          <t>3,81; 11,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 16,41</t>
+          <t>7,07; 15,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,83</t>
+          <t>2,57; 9,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,24; 17,58</t>
+          <t>8,62; 18,58</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 14,68</t>
+          <t>4,43; 15,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 10,98</t>
+          <t>2,02; 11,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 19,06</t>
+          <t>6,53; 19,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 21,89</t>
+          <t>7,01; 22,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 15,77</t>
+          <t>4,97; 15,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 16,83</t>
+          <t>4,6; 16,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 18,87</t>
+          <t>6,63; 18,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 58,69</t>
+          <t>13,39; 55,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 13,34</t>
+          <t>5,95; 13,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,92</t>
+          <t>4,03; 11,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 16,32</t>
+          <t>7,93; 17,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 39,21</t>
+          <t>12,57; 41,06</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 23,25</t>
+          <t>5,69; 25,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 22,77</t>
+          <t>5,17; 22,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,86</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 19,67</t>
+          <t>3,15; 17,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 20,75</t>
+          <t>4,63; 20,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,57; 31,14</t>
+          <t>11,01; 29,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,36</t>
+          <t>0,0; 8,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 20,31</t>
+          <t>4,6; 19,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 17,98</t>
+          <t>7,05; 18,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 23,43</t>
+          <t>10,69; 22,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,56</t>
+          <t>0,67; 5,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 15,38</t>
+          <t>5,31; 15,65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 9,91</t>
+          <t>1,2; 9,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 18,47</t>
+          <t>5,07; 19,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 21,94</t>
+          <t>7,31; 21,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,81; 17,03</t>
+          <t>3,82; 17,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 15,77</t>
+          <t>4,17; 16,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,0; 23,75</t>
+          <t>8,75; 24,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 23,12</t>
+          <t>7,14; 22,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,87; 30,29</t>
+          <t>13,12; 29,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,51</t>
+          <t>3,42; 10,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,07; 18,52</t>
+          <t>8,4; 18,62</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,48; 19,91</t>
+          <t>8,98; 20,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,51; 21,81</t>
+          <t>10,6; 21,35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 12,57</t>
+          <t>4,36; 12,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 14,43</t>
+          <t>5,88; 13,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,57</t>
+          <t>2,89; 9,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 12,8</t>
+          <t>4,99; 13,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 16,08</t>
+          <t>7,43; 16,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 17,22</t>
+          <t>8,45; 17,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,96</t>
+          <t>3,66; 10,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,32; 20,14</t>
+          <t>9,55; 20,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 12,79</t>
+          <t>6,82; 12,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,99; 14,27</t>
+          <t>8,11; 14,06</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,73</t>
+          <t>3,73; 8,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,45; 15,63</t>
+          <t>8,35; 15,54</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,42; 11,22</t>
+          <t>4,28; 11,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,76</t>
+          <t>7,65; 15,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,95</t>
+          <t>2,77; 8,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,33</t>
+          <t>3,61; 11,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,94; 18,84</t>
+          <t>9,51; 18,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,27; 17,83</t>
+          <t>9,42; 18,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,6</t>
+          <t>2,65; 8,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,9</t>
+          <t>2,79; 8,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,07; 13,62</t>
+          <t>8,17; 13,67</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,69; 15,29</t>
+          <t>9,42; 15,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,85</t>
+          <t>3,28; 6,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,67</t>
+          <t>3,76; 8,3</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,17</t>
+          <t>6,51; 10,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,9; 13,54</t>
+          <t>9,95; 13,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,49</t>
+          <t>5,29; 8,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,45</t>
+          <t>7,47; 12,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,54</t>
+          <t>9,66; 13,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,64</t>
+          <t>11,64; 15,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,51</t>
+          <t>5,56; 8,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,49; 17,19</t>
+          <t>10,61; 17,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,32</t>
+          <t>8,77; 11,41</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,32; 14,19</t>
+          <t>11,25; 14,17</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,07</t>
+          <t>5,73; 7,91</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,07</t>
+          <t>9,69; 14,64</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5825</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14661</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6922</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13229</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11349</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17869</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8986</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13709</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>17174</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32530</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15908</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>26938</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3102; 10311</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9808; 20324</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3520; 11753</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6271; 30733</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7218; 17918</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12180; 25145</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5153; 14652</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8250; 21139</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>11335; 23826</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>24645; 41149</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10290; 22937</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>17726; 45173</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10086</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12013</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3632</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7690</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11788</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11910</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8762</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>21873</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23923</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7036</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>16451</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5975; 15434</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7709; 18396</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1224; 7307</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3009; 13689</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7210; 17179</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7576; 17804</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1293; 7514</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4776; 15385</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>15359; 30377</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>17334; 32590</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3658; 12083</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9670; 24657</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9253</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4657</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5045</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6155</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8494</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10166</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15409</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7367</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>15698</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2033; 9869</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5481; 15119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2076; 9527</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4098; 12679</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1893; 9423</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3338; 10989</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>655; 6232</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4500; 13764</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5259; 15241</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9853; 22210</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3511; 12947</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>10809; 23308</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6611</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4217</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9126</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9286</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7477</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7755</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9566</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>22202</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14088</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11972</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18692</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>31488</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3320; 11274</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1569; 8680</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5023; 14827</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4915; 16023</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3934; 12438</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3784; 13539</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5380; 15248</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>10463; 43544</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9158; 20338</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>6441; 18883</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>12541; 27029</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>18634; 60880</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5237</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5355</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4151</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>10122</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14505</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>7351</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2383; 10513</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2268; 9878</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3060</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1086; 6168</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2078; 9136</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5149; 13809</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3929</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1872; 8140</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>6116; 16240</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>9695; 20761</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>598; 5123</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3994; 11771</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7362</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4181</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>9062</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7957</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>11549</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7092</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>14882</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>15319</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>15730</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>670; 5525</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2840; 10814</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3967; 11864</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1764; 8018</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2494; 10021</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>5274; 14838</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4068; 12950</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>7372; 16734</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3965; 11664</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>9765; 21646</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>9991; 22318</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>10851; 21857</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>9788</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12970</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7395</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10428</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>15063</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>17850</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>9196</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>22100</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>24851</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>30819</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>16591</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>32528</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5608; 16130</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>8161; 18934</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3971; 12592</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6208; 16373</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>10076; 22263</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>12320; 25162</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5254; 15137</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>14815; 31879</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>18026; 33748</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>23061; 39997</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>10480; 23109</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>23361; 43473</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>11499</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>18581</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7947</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>8330</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>22855</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>22668</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8367</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>8063</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>34353</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>41249</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>16314</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>16393</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>6755; 17560</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>12546; 26029</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>4541; 13398</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>4734; 14424</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>15534; 29925</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>16144; 31055</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4524; 13771</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>4344; 13931</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>26255; 43920</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>31585; 52669</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>10977; 22833</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>10791; 23800</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>56243</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>82869</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>47647</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>63548</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>99029</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>139721</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>185289</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>99093</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>162578</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>44360; 69145</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>70716; 97881</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>37149; 58633</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>49681; 83860</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>69713; 97968</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>87689; 118812</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>41248; 63708</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>80646; 131983</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>123077; 160145</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>164766; 207436</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>82772; 114153</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>138048; 208543</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 19,61</t>
+          <t>5,04; 19,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,08; 35,39</t>
+          <t>17,81; 37,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 20,94</t>
+          <t>5,98; 20,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 41,94</t>
+          <t>8,37; 40,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,99; 29,76</t>
+          <t>11,45; 28,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 38,8</t>
+          <t>18,91; 39,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 22,73</t>
+          <t>7,51; 22,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 26,63</t>
+          <t>10,28; 27,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,05; 21,13</t>
+          <t>10,5; 21,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,16; 33,66</t>
+          <t>19,91; 33,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,53; 19,02</t>
+          <t>8,56; 18,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 29,59</t>
+          <t>11,56; 29,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 15,2</t>
+          <t>5,76; 15,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 17,57</t>
+          <t>7,15; 17,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,09</t>
+          <t>1,18; 7,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,79</t>
+          <t>2,43; 11,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 15,8</t>
+          <t>6,64; 16,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 16,02</t>
+          <t>6,55; 15,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,91</t>
+          <t>1,18; 7,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,06</t>
+          <t>3,72; 11,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 14,44</t>
+          <t>7,42; 14,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 15,1</t>
+          <t>7,84; 14,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,71</t>
+          <t>1,79; 5,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 9,69</t>
+          <t>3,9; 9,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 14,6</t>
+          <t>3,44; 14,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 22,18</t>
+          <t>7,75; 21,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,26</t>
+          <t>2,49; 13,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 21,76</t>
+          <t>6,63; 20,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 13,4</t>
+          <t>3,53; 13,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 15,42</t>
+          <t>3,93; 15,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,91</t>
+          <t>0,96; 8,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 20,49</t>
+          <t>7,05; 21,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 11,05</t>
+          <t>4,38; 12,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 15,93</t>
+          <t>7,01; 16,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,47</t>
+          <t>2,65; 9,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,62; 18,58</t>
+          <t>8,33; 18,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 15,06</t>
+          <t>4,67; 15,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,16</t>
+          <t>2,37; 11,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 19,27</t>
+          <t>6,75; 19,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 22,84</t>
+          <t>7,04; 21,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 15,72</t>
+          <t>5,1; 16,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 16,46</t>
+          <t>4,57; 17,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 18,78</t>
+          <t>6,36; 20,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,39; 55,73</t>
+          <t>12,83; 57,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,21</t>
+          <t>5,67; 13,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 11,8</t>
+          <t>4,5; 11,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 17,09</t>
+          <t>7,93; 16,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,57; 41,06</t>
+          <t>12,74; 41,52</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 25,12</t>
+          <t>5,15; 23,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 22,5</t>
+          <t>5,23; 22,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 17,87</t>
+          <t>3,96; 19,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 20,37</t>
+          <t>4,66; 20,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,01; 29,54</t>
+          <t>11,33; 30,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,48</t>
+          <t>0,0; 9,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 19,99</t>
+          <t>3,96; 19,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 18,73</t>
+          <t>6,59; 18,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,69; 22,9</t>
+          <t>11,16; 24,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,71</t>
+          <t>0,67; 5,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 15,65</t>
+          <t>5,7; 15,94</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 9,86</t>
+          <t>1,18; 9,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 19,32</t>
+          <t>5,18; 18,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,31; 21,86</t>
+          <t>7,29; 22,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,82; 17,37</t>
+          <t>3,85; 17,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 16,78</t>
+          <t>4,1; 15,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,75; 24,63</t>
+          <t>8,77; 23,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,14; 22,74</t>
+          <t>7,31; 23,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,12; 29,78</t>
+          <t>13,28; 30,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,07</t>
+          <t>3,21; 10,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,4; 18,62</t>
+          <t>8,59; 19,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 20,07</t>
+          <t>8,79; 19,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 21,35</t>
+          <t>10,56; 21,83</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 12,54</t>
+          <t>4,26; 12,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 13,65</t>
+          <t>5,88; 14,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,17</t>
+          <t>2,83; 9,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 13,15</t>
+          <t>4,86; 13,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,43; 16,41</t>
+          <t>7,0; 16,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,45; 17,27</t>
+          <t>8,21; 17,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,56</t>
+          <t>3,59; 10,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 20,54</t>
+          <t>9,35; 20,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 12,77</t>
+          <t>6,86; 12,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,11; 14,06</t>
+          <t>7,91; 13,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,23</t>
+          <t>3,7; 8,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,35; 15,54</t>
+          <t>8,07; 15,43</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 11,12</t>
+          <t>4,57; 11,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,87</t>
+          <t>7,61; 15,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,16</t>
+          <t>2,69; 8,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,0</t>
+          <t>3,51; 10,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,51; 18,32</t>
+          <t>10,02; 18,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,42; 18,13</t>
+          <t>9,35; 17,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,06</t>
+          <t>2,71; 8,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 8,95</t>
+          <t>2,52; 8,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 13,67</t>
+          <t>8,08; 13,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,42; 15,71</t>
+          <t>9,75; 15,48</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,82</t>
+          <t>3,27; 6,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,3</t>
+          <t>3,83; 8,31</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,15</t>
+          <t>6,68; 10,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,77</t>
+          <t>9,79; 13,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,35</t>
+          <t>5,3; 8,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,61</t>
+          <t>7,39; 12,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 13,57</t>
+          <t>9,63; 13,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,77</t>
+          <t>11,61; 15,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,59</t>
+          <t>5,45; 8,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,37</t>
+          <t>10,59; 17,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,41</t>
+          <t>8,62; 11,39</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,17</t>
+          <t>11,23; 14,05</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,91</t>
+          <t>5,76; 8,02</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,64</t>
+          <t>9,66; 14,09</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3102; 10311</t>
+          <t>2650; 10053</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9808; 20324</t>
+          <t>10225; 21409</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3520; 11753</t>
+          <t>3359; 11636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6271; 30733</t>
+          <t>6131; 29365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7218; 17918</t>
+          <t>6895; 17031</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12180; 25145</t>
+          <t>12254; 25476</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5153; 14652</t>
+          <t>4843; 14257</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8250; 21139</t>
+          <t>8162; 21622</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11335; 23826</t>
+          <t>11847; 23936</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24645; 41149</t>
+          <t>24338; 41480</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10290; 22937</t>
+          <t>10322; 22552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17726; 45173</t>
+          <t>17645; 44760</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5975; 15434</t>
+          <t>5853; 16037</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7709; 18396</t>
+          <t>7490; 18202</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1224; 7307</t>
+          <t>1217; 7357</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3009; 13689</t>
+          <t>3085; 13959</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7210; 17179</t>
+          <t>7220; 17959</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7576; 17804</t>
+          <t>7285; 17777</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1293; 7514</t>
+          <t>1282; 7656</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4776; 15385</t>
+          <t>4746; 14981</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15359; 30377</t>
+          <t>15602; 29856</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17334; 32590</t>
+          <t>16920; 31613</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3658; 12083</t>
+          <t>3792; 12266</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9670; 24657</t>
+          <t>9920; 24337</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2033; 9869</t>
+          <t>2324; 9830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5481; 15119</t>
+          <t>5281; 14886</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2076; 9527</t>
+          <t>1665; 9235</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4098; 12679</t>
+          <t>3862; 11825</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1893; 9423</t>
+          <t>2484; 9464</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3338; 10989</t>
+          <t>2799; 10960</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>655; 6232</t>
+          <t>670; 6279</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4500; 13764</t>
+          <t>4735; 14252</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5259; 15241</t>
+          <t>6041; 16568</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9853; 22210</t>
+          <t>9773; 22437</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3511; 12947</t>
+          <t>3626; 13556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10809; 23308</t>
+          <t>10448; 22941</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3320; 11274</t>
+          <t>3495; 11412</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1569; 8680</t>
+          <t>1840; 8807</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5023; 14827</t>
+          <t>5193; 14662</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4915; 16023</t>
+          <t>4938; 14972</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3934; 12438</t>
+          <t>4032; 13095</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3784; 13539</t>
+          <t>3761; 13993</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5380; 15248</t>
+          <t>5162; 16305</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10463; 43544</t>
+          <t>10022; 45246</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9158; 20338</t>
+          <t>8726; 20933</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6441; 18883</t>
+          <t>7192; 18864</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12541; 27029</t>
+          <t>12539; 26794</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18634; 60880</t>
+          <t>18897; 61563</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2383; 10513</t>
+          <t>2157; 10016</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2268; 9878</t>
+          <t>2295; 9925</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3060</t>
+          <t>0; 3213</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1086; 6168</t>
+          <t>1366; 6770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2078; 9136</t>
+          <t>2091; 9062</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5149; 13809</t>
+          <t>5297; 14286</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3929</t>
+          <t>0; 4562</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1872; 8140</t>
+          <t>1611; 8123</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6116; 16240</t>
+          <t>5713; 15889</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9695; 20761</t>
+          <t>10113; 22003</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>598; 5123</t>
+          <t>597; 5133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3994; 11771</t>
+          <t>4289; 11993</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>670; 5525</t>
+          <t>664; 5529</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2840; 10814</t>
+          <t>2900; 10300</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3967; 11864</t>
+          <t>3957; 12299</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1764; 8018</t>
+          <t>1777; 8165</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2494; 10021</t>
+          <t>2451; 9538</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5274; 14838</t>
+          <t>5284; 14295</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4068; 12950</t>
+          <t>4161; 13526</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7372; 16734</t>
+          <t>7464; 16996</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3965; 11664</t>
+          <t>3715; 11702</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9765; 21646</t>
+          <t>9982; 22672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9991; 22318</t>
+          <t>9781; 21740</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10851; 21857</t>
+          <t>10809; 22345</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5608; 16130</t>
+          <t>5482; 15708</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8161; 18934</t>
+          <t>8160; 19644</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3971; 12592</t>
+          <t>3893; 12595</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6208; 16373</t>
+          <t>6052; 17089</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10076; 22263</t>
+          <t>9502; 21792</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12320; 25162</t>
+          <t>11967; 24897</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5254; 15137</t>
+          <t>5150; 14700</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14815; 31879</t>
+          <t>14513; 32108</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18026; 33748</t>
+          <t>18122; 33372</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23061; 39997</t>
+          <t>22499; 39717</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10480; 23109</t>
+          <t>10399; 23044</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23361; 43473</t>
+          <t>22569; 43151</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6755; 17560</t>
+          <t>7209; 17930</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12546; 26029</t>
+          <t>12479; 25948</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4541; 13398</t>
+          <t>4415; 13241</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4734; 14424</t>
+          <t>4600; 13224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15534; 29925</t>
+          <t>16362; 30537</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16144; 31055</t>
+          <t>16019; 30093</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4524; 13771</t>
+          <t>4629; 13793</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4344; 13931</t>
+          <t>3920; 13928</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>26255; 43920</t>
+          <t>25949; 43625</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31585; 52669</t>
+          <t>32696; 51896</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10977; 22833</t>
+          <t>10964; 22987</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10791; 23800</t>
+          <t>10975; 23836</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>44360; 69145</t>
+          <t>45465; 68573</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70716; 97881</t>
+          <t>69593; 97242</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37149; 58633</t>
+          <t>37234; 59554</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49681; 83860</t>
+          <t>49148; 82883</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>69713; 97968</t>
+          <t>69555; 98523</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87689; 118812</t>
+          <t>87486; 116351</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41248; 63708</t>
+          <t>40454; 62554</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>80646; 131983</t>
+          <t>80504; 133640</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>123077; 160145</t>
+          <t>120983; 159801</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>164766; 207436</t>
+          <t>164447; 205744</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82772; 114153</t>
+          <t>83244; 115865</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>138048; 208543</t>
+          <t>137584; 200782</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13,94%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11,08%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>25,53%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12,33%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,05%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,94%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 19,12</t>
+          <t>11,4; 28,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 37,28</t>
+          <t>18,16; 37,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 20,73</t>
+          <t>8,12; 22,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 40,07</t>
+          <t>10,59; 26,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,45; 28,28</t>
+          <t>5,14; 19,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,91; 39,31</t>
+          <t>17,25; 35,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,12</t>
+          <t>6,39; 21,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 27,24</t>
+          <t>7,17; 22,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,5; 21,22</t>
+          <t>9,91; 21,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,91; 33,93</t>
+          <t>19,76; 33,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 18,7</t>
+          <t>9,1; 19,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 29,32</t>
+          <t>11,1; 22,14</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,93%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,47%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,53%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 15,79</t>
+          <t>6,67; 16,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 17,38</t>
+          <t>6,78; 16,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,14</t>
+          <t>1,25; 7,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 11,01</t>
+          <t>3,35; 11,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 16,51</t>
+          <t>5,91; 15,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 15,99</t>
+          <t>6,74; 16,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,04</t>
+          <t>1,2; 7,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 11,74</t>
+          <t>4,07; 13,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 14,2</t>
+          <t>7,0; 13,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 14,64</t>
+          <t>7,95; 14,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,79</t>
+          <t>1,75; 5,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,57</t>
+          <t>4,47; 10,56</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7,58%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,57%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,97%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 14,54</t>
+          <t>3,54; 13,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 21,83</t>
+          <t>4,66; 15,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 13,82</t>
+          <t>1,0; 9,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 20,29</t>
+          <t>6,53; 20,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 13,46</t>
+          <t>3,26; 15,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 15,38</t>
+          <t>8,15; 22,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,98</t>
+          <t>2,77; 14,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 21,22</t>
+          <t>6,11; 19,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 12,01</t>
+          <t>4,36; 11,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 16,09</t>
+          <t>7,12; 16,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,91</t>
+          <t>2,74; 9,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 18,29</t>
+          <t>7,82; 17,07</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26,9%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,83%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,86%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 15,24</t>
+          <t>5,0; 15,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 11,33</t>
+          <t>4,78; 16,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 19,05</t>
+          <t>6,9; 18,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 21,35</t>
+          <t>13,17; 55,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 16,55</t>
+          <t>4,63; 14,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 17,02</t>
+          <t>2,42; 10,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 20,08</t>
+          <t>7,05; 19,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,83; 57,91</t>
+          <t>7,92; 23,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 13,6</t>
+          <t>5,84; 13,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 11,79</t>
+          <t>4,58; 11,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,94</t>
+          <t>7,62; 16,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,74; 41,52</t>
+          <t>13,03; 36,84</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,57%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>12,51%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,2%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 23,93</t>
+          <t>4,69; 20,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 22,61</t>
+          <t>11,57; 31,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,4</t>
+          <t>0,0; 8,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 19,62</t>
+          <t>4,42; 20,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 20,21</t>
+          <t>5,67; 23,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,33; 30,56</t>
+          <t>5,32; 22,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,84</t>
+          <t>0,0; 7,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 19,95</t>
+          <t>4,18; 20,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 18,33</t>
+          <t>6,76; 17,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 24,27</t>
+          <t>10,5; 23,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,72</t>
+          <t>0,66; 5,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 15,94</t>
+          <t>5,46; 15,47</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13,97%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19,63%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3,7%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>10,4%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>13,57%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,97%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,86</t>
+          <t>4,13; 15,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 18,4</t>
+          <t>8,0; 23,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 22,66</t>
+          <t>6,86; 23,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 17,69</t>
+          <t>13,23; 29,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,1; 15,97</t>
+          <t>1,19; 9,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,77; 23,73</t>
+          <t>5,07; 18,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,31; 23,75</t>
+          <t>7,54; 21,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,28; 30,25</t>
+          <t>4,14; 17,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 10,11</t>
+          <t>3,31; 10,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,59; 19,51</t>
+          <t>8,07; 18,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,79; 19,55</t>
+          <t>9,48; 19,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,56; 21,83</t>
+          <t>10,25; 21,46</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12,25%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7,61%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9,35%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,38%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 12,21</t>
+          <t>7,25; 16,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 14,16</t>
+          <t>8,48; 17,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 9,17</t>
+          <t>3,62; 9,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 13,73</t>
+          <t>10,08; 21,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,0; 16,06</t>
+          <t>4,46; 12,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 17,08</t>
+          <t>5,9; 14,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,25</t>
+          <t>2,9; 9,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 20,69</t>
+          <t>5,08; 13,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,63</t>
+          <t>6,79; 12,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,91; 13,96</t>
+          <t>7,99; 14,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,21</t>
+          <t>3,89; 8,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,07; 15,43</t>
+          <t>8,59; 16,0</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>7,28%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>11,33%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>4,84%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 11,36</t>
+          <t>9,94; 18,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,61; 15,82</t>
+          <t>9,27; 17,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 8,07</t>
+          <t>2,85; 8,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,08</t>
+          <t>2,89; 9,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,02; 18,69</t>
+          <t>4,42; 11,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,57</t>
+          <t>7,84; 15,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 8,07</t>
+          <t>2,71; 7,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,95</t>
+          <t>3,15; 9,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,08; 13,58</t>
+          <t>8,07; 13,62</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,75; 15,48</t>
+          <t>9,69; 15,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,86</t>
+          <t>3,19; 6,85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,31</t>
+          <t>3,77; 8,54</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>6,79%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,07</t>
+          <t>9,79; 13,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,68</t>
+          <t>11,36; 15,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,48</t>
+          <t>5,57; 8,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,47</t>
+          <t>10,22; 16,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,63; 13,65</t>
+          <t>6,7; 10,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,61; 15,44</t>
+          <t>9,9; 13,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,43</t>
+          <t>5,26; 8,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,59; 17,58</t>
+          <t>7,63; 11,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,62; 11,39</t>
+          <t>8,77; 11,32</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,23; 14,05</t>
+          <t>11,32; 14,19</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,02</t>
+          <t>5,86; 8,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,09</t>
+          <t>9,47; 13,49</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11349</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17869</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8986</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11546</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5825</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>14661</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6922</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13229</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11349</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17869</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8986</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26938</t>
+          <t>19277</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2650; 10053</t>
+          <t>6862; 17321</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10225; 21409</t>
+          <t>11773; 24576</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3359; 11636</t>
+          <t>5231; 14331</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6131; 29365</t>
+          <t>6794; 16709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6895; 17031</t>
+          <t>2700; 10126</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12254; 25476</t>
+          <t>9904; 20272</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4843; 14257</t>
+          <t>3587; 11789</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8162; 21622</t>
+          <t>4049; 12501</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11847; 23936</t>
+          <t>11179; 23866</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24338; 41480</t>
+          <t>24149; 40404</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10322; 22552</t>
+          <t>10975; 23157</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17645; 44760</t>
+          <t>13392; 26712</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11788</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11910</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7486</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10086</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12013</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3632</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7690</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11788</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11910</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>15352</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5853; 16037</t>
+          <t>7253; 17707</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7490; 18202</t>
+          <t>7540; 18690</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1217; 7357</t>
+          <t>1359; 7680</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3085; 13959</t>
+          <t>3878; 12830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7220; 17959</t>
+          <t>6007; 15768</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7285; 17777</t>
+          <t>7060; 17386</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1282; 7656</t>
+          <t>1235; 7814</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4746; 14981</t>
+          <t>4091; 13503</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15602; 29856</t>
+          <t>14713; 28810</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16920; 31613</t>
+          <t>17157; 32265</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3792; 12266</t>
+          <t>3705; 12468</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9920; 24337</t>
+          <t>9682; 22844</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5045</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6155</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5122</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9253</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4657</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7204</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5045</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6155</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2710</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>13897</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2324; 9830</t>
+          <t>2492; 9421</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5281; 14886</t>
+          <t>3323; 11069</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1665; 9235</t>
+          <t>700; 6818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3862; 11825</t>
+          <t>3877; 12142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2484; 9464</t>
+          <t>2202; 10158</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2799; 10960</t>
+          <t>5554; 15524</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>670; 6279</t>
+          <t>1852; 9570</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4735; 14252</t>
+          <t>3453; 10953</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6041; 16568</t>
+          <t>6018; 16282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9773; 22437</t>
+          <t>9931; 22877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3626; 13556</t>
+          <t>3751; 13447</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10448; 22941</t>
+          <t>9064; 19786</t>
         </is>
       </c>
     </row>
@@ -2702,37 +2702,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7477</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7755</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9566</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19408</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6611</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4217</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9286</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7477</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7755</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9566</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22202</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31488</t>
+          <t>29532</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3495; 11412</t>
+          <t>3954; 12475</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1840; 8807</t>
+          <t>3935; 13840</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5193; 14662</t>
+          <t>5601; 15318</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4938; 14972</t>
+          <t>9506; 39953</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4032; 13095</t>
+          <t>3468; 10991</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3761; 13993</t>
+          <t>1881; 8536</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5162; 16305</t>
+          <t>5422; 14666</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10022; 45246</t>
+          <t>5609; 16684</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8726; 20933</t>
+          <t>8992; 20534</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7192; 18864</t>
+          <t>7326; 19073</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12539; 26794</t>
+          <t>12053; 25805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18897; 61563</t>
+          <t>18637; 52686</t>
         </is>
       </c>
     </row>
@@ -2910,37 +2910,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4135</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>5237</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>5355</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3200</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4885</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9150</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7476</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2157; 10016</t>
+          <t>2105; 9305</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2295; 9925</t>
+          <t>5410; 14558</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3213</t>
+          <t>0; 3874</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1366; 6770</t>
+          <t>1749; 8129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2091; 9062</t>
+          <t>2372; 9729</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5297; 14286</t>
+          <t>2337; 9996</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4562</t>
+          <t>0; 3414</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1611; 8123</t>
+          <t>1488; 7145</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5713; 15889</t>
+          <t>5863; 15584</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10113; 22003</t>
+          <t>9519; 21241</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>597; 5133</t>
+          <t>592; 4996</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4289; 11993</t>
+          <t>4104; 11632</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9062</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7957</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9608</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2076</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5820</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>7362</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4181</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5016</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9062</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7957</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>14087</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>664; 5529</t>
+          <t>2468; 9419</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2900; 10300</t>
+          <t>4822; 14308</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3957; 12299</t>
+          <t>3907; 13166</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1777; 8165</t>
+          <t>6477; 14489</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2451; 9538</t>
+          <t>665; 5556</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5284; 14295</t>
+          <t>2838; 10342</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4161; 13526</t>
+          <t>4093; 11907</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7464; 16996</t>
+          <t>1893; 8211</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3715; 11702</t>
+          <t>3828; 12168</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9982; 22672</t>
+          <t>9383; 21531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9781; 21740</t>
+          <t>10547; 22146</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10809; 22345</t>
+          <t>9710; 20328</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>15063</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>17850</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9196</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>9788</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>12970</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>7395</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>10428</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>15063</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>17850</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9196</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>22100</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>31749</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5482; 15708</t>
+          <t>9837; 21816</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8160; 19644</t>
+          <t>12359; 25096</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3893; 12595</t>
+          <t>5192; 14281</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6052; 17089</t>
+          <t>14156; 30023</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9502; 21792</t>
+          <t>5738; 16164</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11967; 24897</t>
+          <t>8188; 20020</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5150; 14700</t>
+          <t>3983; 13151</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14513; 32108</t>
+          <t>6223; 16575</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18122; 33372</t>
+          <t>17940; 33806</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22499; 39717</t>
+          <t>22725; 40582</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10399; 23044</t>
+          <t>10929; 24516</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>22569; 43151</t>
+          <t>22593; 42097</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>22855</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>22668</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>8367</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>8309</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>11499</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>18581</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>7947</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>8330</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>22855</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>22668</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>8367</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16393</t>
+          <t>16585</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7209; 17930</t>
+          <t>16237; 30780</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12479; 25948</t>
+          <t>15880; 30538</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4415; 13241</t>
+          <t>4870; 14687</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4600; 13224</t>
+          <t>4561; 14543</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>16362; 30537</t>
+          <t>6984; 17724</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16019; 30093</t>
+          <t>12859; 25841</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4629; 13793</t>
+          <t>4453; 13059</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3920; 13928</t>
+          <t>4414; 13778</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25949; 43625</t>
+          <t>25917; 43744</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32696; 51896</t>
+          <t>32478; 51267</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10964; 22987</t>
+          <t>10672; 22945</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10975; 23836</t>
+          <t>11231; 25456</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>47647</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>45465; 68573</t>
+          <t>70691; 97757</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69593; 97242</t>
+          <t>85622; 117859</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37234; 59554</t>
+          <t>41347; 63119</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49148; 82883</t>
+          <t>71419; 114800</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>69555; 98523</t>
+          <t>45625; 69264</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87486; 116351</t>
+          <t>70360; 96227</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40454; 62554</t>
+          <t>36956; 59632</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>80504; 133640</t>
+          <t>47941; 71961</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>120983; 159801</t>
+          <t>122977; 158856</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>164447; 205744</t>
+          <t>165806; 207696</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>83244; 115865</t>
+          <t>84660; 116464</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>137584; 200782</t>
+          <t>125646; 178982</t>
         </is>
       </c>
     </row>
